--- a/frontend/public/templates/awards-import-template.xlsx
+++ b/frontend/public/templates/awards-import-template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,11 +29,7 @@
     <font>
       <b val="1"/>
       <color rgb="001F3D2B"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0000873C"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
@@ -53,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -61,35 +57,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00E5E7EB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00E5E7EB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E5E7EB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E5E7EB"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -457,10 +437,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="105" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,30 +458,23 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>1. 第二个 sheet 的列与“门户内容 - 获奖成果 - 新增获奖”表单对应，请从第 2 行开始填写。</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1. 奖项名称必填。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>2. 必填：奖项名称。系统按奖项名称和获奖日期更新已有获奖成果。</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2. 奖项等级可以写授奖单位 + 奖项等级，保持简洁即可。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>3. 获奖图片列用于放图片：可在对应行插入一张获奖图片，系统会读取该行第一张图片；获奖图片列里的文字不会被导入。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>4. 附件 PDF 列只作提醒；批量导入先导入文字信息，PDF 或其它附件请在单条获奖成果编辑页面上传。</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>3. 首页排序默认 0。</t>
         </is>
       </c>
     </row>
@@ -519,115 +492,110 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>奖项名称</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>奖项等级</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>获奖日期</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>参与人员</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>可见范围</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>获奖图片</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>附件PDF</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>可见范围</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>首页排序</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>示例获奖成果</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>一等奖</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>团队成员</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>城乡有机废弃物高效快速堆肥关键技术与设备研发及应用</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>中国环保产业协会环境技术进步奖一等奖</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>李季，韩跃国，魏雨泉等</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>公开</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>排名第3/15；简短说明。</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>可在本行插入获奖图片</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>导入后在单条获奖中上传附件</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>公开</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>填写获奖说明。</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>10</v>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"公开,成员可见,管理员可见"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/frontend/public/templates/awards-import-template.xlsx
+++ b/frontend/public/templates/awards-import-template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,7 +29,11 @@
     <font>
       <b val="1"/>
       <color rgb="001F3D2B"/>
-      <sz val="14"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000873C"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +53,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,19 +61,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -437,10 +457,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,23 +478,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>1. 奖项名称必填。</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1. 第二个 sheet 的列与“门户内容 - 获奖成果 - 新增获奖”表单对应，请从第 2 行开始填写。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2. 奖项等级可以写授奖单位 + 奖项等级，保持简洁即可。</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2. 必填：奖项名称。系统按奖项名称和获奖日期更新已有获奖成果。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>3. 首页排序默认 0。</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>3. 获奖图片列用于放图片：可在对应行插入一张获奖图片，系统会读取该行第一张图片；获奖图片列里的文字不会被导入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>4. 附件 PDF 列只作提醒；批量导入先导入文字信息，PDF 或其它附件请在单条获奖成果编辑页面上传。</t>
         </is>
       </c>
     </row>
@@ -492,110 +519,115 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>奖项名称</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>奖项等级</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>获奖日期</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>参与人员</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>获奖图片</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>附件PDF</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>可见范围</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>获奖图片</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>附件PDF</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>首页排序</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>城乡有机废弃物高效快速堆肥关键技术与设备研发及应用</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>中国环保产业协会环境技术进步奖一等奖</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>李季，韩跃国，魏雨泉等</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>示例获奖成果</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>一等奖</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>团队成员</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>可在本行插入获奖图片</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>导入后在单条获奖中上传附件</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>公开</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>排名第3/15；简短说明。</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>可在本行插入获奖图片</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>导入后在单条获奖中上传附件</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>填写获奖说明。</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"公开,成员可见,管理员可见"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>